--- a/artfynd/A 9999-2023 artfynd.xlsx
+++ b/artfynd/A 9999-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125072523</v>
+        <v>125072522</v>
       </c>
       <c r="B2" t="n">
         <v>57454</v>
@@ -761,12 +761,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-03-13</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-03-13</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="AD2" t="b">

--- a/artfynd/A 9999-2023 artfynd.xlsx
+++ b/artfynd/A 9999-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125072522</v>
+        <v>125072511</v>
       </c>
       <c r="B2" t="n">
         <v>57454</v>
@@ -761,12 +761,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="AD2" t="b">

--- a/artfynd/A 9999-2023 artfynd.xlsx
+++ b/artfynd/A 9999-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125072511</v>
+        <v>125072523</v>
       </c>
       <c r="B2" t="n">
         <v>57454</v>
@@ -761,12 +761,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="AD2" t="b">

--- a/artfynd/A 9999-2023 artfynd.xlsx
+++ b/artfynd/A 9999-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125072523</v>
+        <v>125072511</v>
       </c>
       <c r="B2" t="n">
         <v>57454</v>
@@ -761,12 +761,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-03-13</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-03-13</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="AD2" t="b">

--- a/artfynd/A 9999-2023 artfynd.xlsx
+++ b/artfynd/A 9999-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125072511</v>
+        <v>125072522</v>
       </c>
       <c r="B2" t="n">
         <v>57454</v>
@@ -761,12 +761,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="AD2" t="b">

--- a/artfynd/A 9999-2023 artfynd.xlsx
+++ b/artfynd/A 9999-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125072522</v>
+        <v>125072518</v>
       </c>
       <c r="B2" t="n">
-        <v>57454</v>
+        <v>57529</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102622</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Pärluggla</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Aegolius funereus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -793,10 +793,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125072518</v>
+        <v>125072522</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>57454</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,20 +805,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>102622</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Pärluggla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Aegolius funereus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">

--- a/artfynd/A 9999-2023 artfynd.xlsx
+++ b/artfynd/A 9999-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125072518</v>
+        <v>125072511</v>
       </c>
       <c r="B2" t="n">
-        <v>57529</v>
+        <v>57454</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>102622</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Pärluggla</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Aegolius funereus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -761,12 +761,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -793,10 +793,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125072522</v>
+        <v>125072518</v>
       </c>
       <c r="B3" t="n">
-        <v>57454</v>
+        <v>57529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,20 +805,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102622</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Pärluggla</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Aegolius funereus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">

--- a/artfynd/A 9999-2023 artfynd.xlsx
+++ b/artfynd/A 9999-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125072511</v>
+        <v>125072522</v>
       </c>
       <c r="B2" t="n">
-        <v>57454</v>
+        <v>57471</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -761,12 +761,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,7 +796,7 @@
         <v>125072518</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>57632</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
